--- a/premise/data/additional_inventories/lci-vrfb-reference-conditioning.xlsx
+++ b/premise/data/additional_inventories/lci-vrfb-reference-conditioning.xlsx
@@ -437,7 +437,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>vanadium electrolyte conditioning, reference design</t>
+          <t xml:space="preserve">vanadium electrolyte conditioning</t>
         </is>
       </c>
     </row>
@@ -449,7 +449,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>vanadium electrolyte conditioning, reference design</t>
+          <t xml:space="preserve">vanadium electrolyte conditioning</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,8 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VRFB reference correction v1 (2026-10-17). Independent reconstruction: Oxkem VOS16 2024 electrolyte; Martin 2020 electrochemical reduction; Weber 2018 hardware and lifetime. Nominal capacity uses paired one-electron V charge at Li 2011's 1.25 V standard potential, an explicit reference assumption, not a measured discharge average. Legacy '8.3 MWh' activity name is an identifier, not the reconstructed capacity. The source archive's unspecified remaining-error warning is unresolved; no archive processes are copied. See data/battery/vanadium_reference_design.json and stationary battery documentation for calculations and coverage gaps. Fixed design at all years, no imposed primary/secondary-share change. One unit conditions one kg final solution, not one kg material. Water and electricity only here; V2O5/acids are bought by final electrolyte production. Reduction electricity is per kg V. Electrode/membrane wear, peripheral energy and process-factory inventory remain gaps.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: vanadium electrolyte conditioning, reference design. Former reference product: vanadium electrolyte conditioning, reference design. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+VRFB reference correction v1 (2026-10-17). Independent reconstruction: Oxkem VOS16 2024 electrolyte; Martin 2020 electrochemical reduction; Weber 2018 hardware and lifetime. Nominal capacity uses paired one-electron V charge at Li 2011's 1.25 V standard potential, an explicit reference assumption, not a measured discharge average. Legacy '8.3 MWh' activity name is an identifier, not the reconstructed capacity. The source archive's unspecified remaining-error warning is unresolved; no archive processes are copied. See data/battery/vanadium_reference_design.json and stationary battery documentation for calculations and coverage gaps. Fixed design at all years, no imposed primary/secondary-share change. One unit conditions one kg final solution, not one kg material. Water and electricity only here; V2O5/acids are bought by final electrolyte production. Reduction electricity is per kg V. Electrode/membrane wear, peripheral energy and process-factory inventory remain gaps.</t>
         </is>
       </c>
     </row>
@@ -563,7 +564,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>vanadium electrolyte conditioning, reference design</t>
+          <t xml:space="preserve">vanadium electrolyte conditioning</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -586,7 +587,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>vanadium electrolyte conditioning, reference design</t>
+          <t xml:space="preserve">vanadium electrolyte conditioning</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-vrfb-reference-conditioning.xlsx
+++ b/premise/data/additional_inventories/lci-vrfb-reference-conditioning.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilogram</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,8 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: vanadium electrolyte conditioning, reference design. Former reference product: vanadium electrolyte conditioning, reference design. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: Conditioning of one kilogram of final electrolyte solution. Unit field: kilogram. Former reference: 1 unit = 1 kilogram on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+Nomenclature revision, 2026-10-19. Former activity name: vanadium electrolyte conditioning, reference design. Former reference product: vanadium electrolyte conditioning, reference design. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 VRFB reference correction v1 (2026-10-17). Independent reconstruction: Oxkem VOS16 2024 electrolyte; Martin 2020 electrochemical reduction; Weber 2018 hardware and lifetime. Nominal capacity uses paired one-electron V charge at Li 2011's 1.25 V standard potential, an explicit reference assumption, not a measured discharge average. Legacy '8.3 MWh' activity name is an identifier, not the reconstructed capacity. The source archive's unspecified remaining-error warning is unresolved; no archive processes are copied. See data/battery/vanadium_reference_design.json and stationary battery documentation for calculations and coverage gaps. Fixed design at all years, no imposed primary/secondary-share change. One unit conditions one kg final solution, not one kg material. Water and electricity only here; V2O5/acids are bought by final electrolyte production. Reduction electricity is per kg V. Electrode/membrane wear, peripheral energy and process-factory inventory remain gaps.</t>
         </is>
       </c>
@@ -577,7 +578,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilogram</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">

--- a/premise/data/additional_inventories/lci-vrfb-reference-conditioning.xlsx
+++ b/premise/data/additional_inventories/lci-vrfb-reference-conditioning.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,129 +516,112 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Exchanges</t>
+          <t xml:space="preserve">source</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oxkem VOS16 (2024), Martin (2020) and Weber (2018), reconstructed reference documented in premise/data/battery/vanadium_reference_design.json and the activity comment; unvalidated industrial conditioning and treatment proxies remain explicit limitations.
+Explicit reference links (source or inherited supplier evidence; the engineering adaptation is documented in the activity comment): https://zenodo.org/records/10589869 ; https://www.oxkem.com/wp-content/uploads/2025/04/Vanadium-Electrolyte-TDS-1.6mol.L.pdf ; https://d-nb.info/1260641937/34 ; https://www.pnnl.gov/sites/default/files/media/file/at/publications/333_926201145351.pdf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>comment</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">vanadium electrolyte conditioning</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">kilogram</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>categories</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">vanadium electrolyte conditioning</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>market for water, deionised</t>
+          <t xml:space="preserve">vanadium electrolyte conditioning</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6000001816608996</v>
+        <v>1</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Europe without Switzerland</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t xml:space="preserve">kilogram</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>water, deionised</t>
+          <t xml:space="preserve">vanadium electrolyte conditioning</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>market for electricity, medium voltage</t>
+          <t>market for water, deionised</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1012836882352941</v>
+        <v>0.6000001816608996</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>Europe without Switzerland</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>kilowatt hour</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -648,40 +631,70 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Martin 2020 Table 6 / Eq.5: 1.69 kWh/kg elemental V; DE electricity is a location proxy. Excludes peripheral devices.</t>
+          <t>water, deionised</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>market for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.1012836882352941</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Martin 2020 Table 6 / Eq.5: 1.69 kWh/kg elemental V; DE electricity is a location proxy. Excludes peripheral devices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Oxygen</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B16" t="n">
         <v>0.01411676470588235</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>air</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>biosphere</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Stoichiometric OER accompanying V(V) to mean V(III/IV): 1.5 electrons/V, four electrons/O2.</t>
         </is>
